--- a/reports/Debug-snowbowl-20260105/Week Total (Prior Year)_Visits.xlsx
+++ b/reports/Debug-snowbowl-20260105/Week Total (Prior Year)_Visits.xlsx
@@ -37,10 +37,10 @@
     <t>Snowbowl Comp Tickets</t>
   </si>
   <si>
-    <t>Snowbowl Passes</t>
+    <t>Snowbowl Uplift Tickets</t>
   </si>
   <si>
-    <t>Snowbowl Uplift Tickets</t>
+    <t>Snowbowl Passes</t>
   </si>
 </sst>
 </file>
@@ -473,13 +473,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2">
-        <v>45663</v>
+        <v>45664</v>
       </c>
       <c r="C5" s="2">
-        <v>47</v>
+        <v>161</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -487,13 +487,13 @@
         <v>1</v>
       </c>
       <c r="B6" s="2">
-        <v>45664</v>
+        <v>45667</v>
       </c>
       <c r="C6" s="2">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -501,10 +501,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="2">
-        <v>45665</v>
+        <v>45668</v>
       </c>
       <c r="C7" s="2">
-        <v>7</v>
+        <v>66</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>7</v>
@@ -515,13 +515,13 @@
         <v>1</v>
       </c>
       <c r="B8" s="2">
-        <v>45666</v>
+        <v>45664</v>
       </c>
       <c r="C8" s="2">
-        <v>17</v>
+        <v>565</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -529,13 +529,13 @@
         <v>1</v>
       </c>
       <c r="B9" s="2">
-        <v>45668</v>
+        <v>45664</v>
       </c>
       <c r="C9" s="2">
+        <v>1702</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -543,13 +543,13 @@
         <v>1</v>
       </c>
       <c r="B10" s="2">
-        <v>45669</v>
+        <v>45665</v>
       </c>
       <c r="C10" s="2">
-        <v>63</v>
+        <v>133</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -557,13 +557,13 @@
         <v>1</v>
       </c>
       <c r="B11" s="2">
-        <v>45663</v>
+        <v>45667</v>
       </c>
       <c r="C11" s="2">
         <v>2</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -571,13 +571,13 @@
         <v>1</v>
       </c>
       <c r="B12" s="2">
-        <v>45663</v>
+        <v>45667</v>
       </c>
       <c r="C12" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -585,13 +585,13 @@
         <v>1</v>
       </c>
       <c r="B13" s="2">
-        <v>45665</v>
+        <v>45668</v>
       </c>
       <c r="C13" s="2">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -599,10 +599,10 @@
         <v>1</v>
       </c>
       <c r="B14" s="2">
-        <v>45666</v>
+        <v>45663</v>
       </c>
       <c r="C14" s="2">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>7</v>
@@ -613,13 +613,13 @@
         <v>1</v>
       </c>
       <c r="B15" s="2">
-        <v>45666</v>
+        <v>45664</v>
       </c>
       <c r="C15" s="2">
-        <v>262</v>
+        <v>59</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -627,13 +627,13 @@
         <v>1</v>
       </c>
       <c r="B16" s="2">
-        <v>45668</v>
+        <v>45667</v>
       </c>
       <c r="C16" s="2">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -641,13 +641,13 @@
         <v>1</v>
       </c>
       <c r="B17" s="2">
-        <v>45669</v>
+        <v>45667</v>
       </c>
       <c r="C17" s="2">
-        <v>1282</v>
+        <v>843</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -655,13 +655,13 @@
         <v>1</v>
       </c>
       <c r="B18" s="2">
-        <v>45663</v>
+        <v>45668</v>
       </c>
       <c r="C18" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -669,13 +669,13 @@
         <v>1</v>
       </c>
       <c r="B19" s="2">
-        <v>45663</v>
+        <v>45669</v>
       </c>
       <c r="C19" s="2">
-        <v>287</v>
+        <v>17</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -683,13 +683,13 @@
         <v>1</v>
       </c>
       <c r="B20" s="2">
-        <v>45666</v>
+        <v>45669</v>
       </c>
       <c r="C20" s="2">
-        <v>112</v>
+        <v>185</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -697,13 +697,13 @@
         <v>1</v>
       </c>
       <c r="B21" s="2">
-        <v>45668</v>
+        <v>45663</v>
       </c>
       <c r="C21" s="2">
-        <v>111</v>
+        <v>6</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -711,13 +711,13 @@
         <v>1</v>
       </c>
       <c r="B22" s="2">
-        <v>45669</v>
+        <v>45663</v>
       </c>
       <c r="C22" s="2">
-        <v>1</v>
+        <v>1828</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -725,13 +725,13 @@
         <v>1</v>
       </c>
       <c r="B23" s="2">
-        <v>45669</v>
+        <v>45664</v>
       </c>
       <c r="C23" s="2">
-        <v>868</v>
+        <v>4</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -742,10 +742,10 @@
         <v>45664</v>
       </c>
       <c r="C24" s="2">
-        <v>161</v>
+        <v>90</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -753,13 +753,13 @@
         <v>1</v>
       </c>
       <c r="B25" s="2">
-        <v>45667</v>
+        <v>45665</v>
       </c>
       <c r="C25" s="2">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -767,10 +767,10 @@
         <v>1</v>
       </c>
       <c r="B26" s="2">
-        <v>45668</v>
+        <v>45665</v>
       </c>
       <c r="C26" s="2">
-        <v>66</v>
+        <v>400</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>8</v>
@@ -781,13 +781,13 @@
         <v>1</v>
       </c>
       <c r="B27" s="2">
-        <v>45663</v>
+        <v>45666</v>
       </c>
       <c r="C27" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -795,10 +795,10 @@
         <v>1</v>
       </c>
       <c r="B28" s="2">
-        <v>45663</v>
+        <v>45666</v>
       </c>
       <c r="C28" s="2">
-        <v>1828</v>
+        <v>1552</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>5</v>
@@ -809,13 +809,13 @@
         <v>1</v>
       </c>
       <c r="B29" s="2">
-        <v>45664</v>
+        <v>45667</v>
       </c>
       <c r="C29" s="2">
         <v>4</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -823,10 +823,10 @@
         <v>1</v>
       </c>
       <c r="B30" s="2">
-        <v>45664</v>
+        <v>45668</v>
       </c>
       <c r="C30" s="2">
-        <v>90</v>
+        <v>1152</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>8</v>
@@ -837,13 +837,13 @@
         <v>1</v>
       </c>
       <c r="B31" s="2">
-        <v>45665</v>
+        <v>45669</v>
       </c>
       <c r="C31" s="2">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -851,13 +851,13 @@
         <v>1</v>
       </c>
       <c r="B32" s="2">
-        <v>45665</v>
+        <v>45663</v>
       </c>
       <c r="C32" s="2">
-        <v>400</v>
+        <v>2</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -865,13 +865,13 @@
         <v>1</v>
       </c>
       <c r="B33" s="2">
-        <v>45666</v>
+        <v>45663</v>
       </c>
       <c r="C33" s="2">
-        <v>3</v>
+        <v>749</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -879,13 +879,13 @@
         <v>1</v>
       </c>
       <c r="B34" s="2">
-        <v>45666</v>
+        <v>45665</v>
       </c>
       <c r="C34" s="2">
-        <v>1552</v>
+        <v>0</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -893,13 +893,13 @@
         <v>1</v>
       </c>
       <c r="B35" s="2">
-        <v>45667</v>
+        <v>45666</v>
       </c>
       <c r="C35" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -907,13 +907,13 @@
         <v>1</v>
       </c>
       <c r="B36" s="2">
-        <v>45668</v>
+        <v>45666</v>
       </c>
       <c r="C36" s="2">
-        <v>1152</v>
+        <v>262</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -921,13 +921,13 @@
         <v>1</v>
       </c>
       <c r="B37" s="2">
-        <v>45669</v>
+        <v>45668</v>
       </c>
       <c r="C37" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -935,13 +935,13 @@
         <v>1</v>
       </c>
       <c r="B38" s="2">
-        <v>45664</v>
+        <v>45669</v>
       </c>
       <c r="C38" s="2">
-        <v>565</v>
+        <v>1282</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -949,13 +949,13 @@
         <v>1</v>
       </c>
       <c r="B39" s="2">
-        <v>45664</v>
+        <v>45663</v>
       </c>
       <c r="C39" s="2">
-        <v>1702</v>
+        <v>47</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -963,13 +963,13 @@
         <v>1</v>
       </c>
       <c r="B40" s="2">
-        <v>45665</v>
+        <v>45664</v>
       </c>
       <c r="C40" s="2">
-        <v>133</v>
+        <v>4</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -977,13 +977,13 @@
         <v>1</v>
       </c>
       <c r="B41" s="2">
-        <v>45667</v>
+        <v>45665</v>
       </c>
       <c r="C41" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -991,13 +991,13 @@
         <v>1</v>
       </c>
       <c r="B42" s="2">
-        <v>45667</v>
+        <v>45666</v>
       </c>
       <c r="C42" s="2">
-        <v>751</v>
+        <v>17</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1008,10 +1008,10 @@
         <v>45668</v>
       </c>
       <c r="C43" s="2">
-        <v>254</v>
+        <v>5</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1019,7 +1019,7 @@
         <v>1</v>
       </c>
       <c r="B44" s="2">
-        <v>45663</v>
+        <v>45669</v>
       </c>
       <c r="C44" s="2">
         <v>63</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="B45" s="2">
-        <v>45664</v>
+        <v>45663</v>
       </c>
       <c r="C45" s="2">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1047,13 +1047,13 @@
         <v>1</v>
       </c>
       <c r="B46" s="2">
-        <v>45667</v>
+        <v>45663</v>
       </c>
       <c r="C46" s="2">
-        <v>58</v>
+        <v>287</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1061,13 +1061,13 @@
         <v>1</v>
       </c>
       <c r="B47" s="2">
-        <v>45667</v>
+        <v>45666</v>
       </c>
       <c r="C47" s="2">
-        <v>843</v>
+        <v>112</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1078,10 +1078,10 @@
         <v>45668</v>
       </c>
       <c r="C48" s="2">
-        <v>4</v>
+        <v>111</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1092,10 +1092,10 @@
         <v>45669</v>
       </c>
       <c r="C49" s="2">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1106,10 +1106,10 @@
         <v>45669</v>
       </c>
       <c r="C50" s="2">
-        <v>185</v>
+        <v>868</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
